--- a/output/laminas_comunales/comunal_i_peringrmin_a_2022_araucania.xlsx
+++ b/output/laminas_comunales/comunal_i_peringrmin_a_2022_araucania.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -396,9 +391,6 @@
       <c r="B2">
         <v>12.08</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -409,9 +401,6 @@
       <c r="B3">
         <v>9.890000000000001</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -422,9 +411,6 @@
       <c r="B4">
         <v>9.529999999999999</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -435,9 +421,6 @@
       <c r="B5">
         <v>9.27</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -448,9 +431,6 @@
       <c r="B6">
         <v>8.869999999999999</v>
       </c>
-      <c r="F6" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -461,9 +441,6 @@
       <c r="B7">
         <v>8.76</v>
       </c>
-      <c r="F7" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -474,9 +451,6 @@
       <c r="B8">
         <v>8.67</v>
       </c>
-      <c r="F8" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -487,9 +461,6 @@
       <c r="B9">
         <v>8.23</v>
       </c>
-      <c r="F9" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -500,9 +471,6 @@
       <c r="B10">
         <v>8.19</v>
       </c>
-      <c r="F10" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -513,9 +481,6 @@
       <c r="B11">
         <v>8.1</v>
       </c>
-      <c r="F11" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -526,9 +491,6 @@
       <c r="B12">
         <v>7.76</v>
       </c>
-      <c r="F12" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -539,9 +501,6 @@
       <c r="B13">
         <v>7.75</v>
       </c>
-      <c r="F13" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -552,9 +511,6 @@
       <c r="B14">
         <v>7.62</v>
       </c>
-      <c r="F14" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -565,9 +521,6 @@
       <c r="B15">
         <v>7.42</v>
       </c>
-      <c r="F15" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -578,9 +531,6 @@
       <c r="B16">
         <v>7.24</v>
       </c>
-      <c r="F16" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -591,9 +541,6 @@
       <c r="B17">
         <v>7.04</v>
       </c>
-      <c r="F17" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -604,9 +551,6 @@
       <c r="B18">
         <v>6.84</v>
       </c>
-      <c r="F18" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -617,9 +561,6 @@
       <c r="B19">
         <v>6.81</v>
       </c>
-      <c r="F19" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -630,9 +571,6 @@
       <c r="B20">
         <v>6.73</v>
       </c>
-      <c r="F20" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -643,9 +581,6 @@
       <c r="B21">
         <v>6.37</v>
       </c>
-      <c r="F21" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -656,9 +591,6 @@
       <c r="B22">
         <v>6.27</v>
       </c>
-      <c r="F22" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -669,9 +601,6 @@
       <c r="B23">
         <v>6.27</v>
       </c>
-      <c r="F23" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -682,9 +611,6 @@
       <c r="B24">
         <v>6.2</v>
       </c>
-      <c r="F24" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -695,9 +621,6 @@
       <c r="B25">
         <v>6.17</v>
       </c>
-      <c r="F25" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -708,9 +631,6 @@
       <c r="B26">
         <v>6.05</v>
       </c>
-      <c r="F26" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -721,9 +641,6 @@
       <c r="B27">
         <v>5.76</v>
       </c>
-      <c r="F27" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -734,9 +651,6 @@
       <c r="B28">
         <v>5.21</v>
       </c>
-      <c r="F28" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -747,9 +661,6 @@
       <c r="B29">
         <v>5.18</v>
       </c>
-      <c r="F29" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -760,9 +671,6 @@
       <c r="B30">
         <v>5.09</v>
       </c>
-      <c r="F30" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -773,9 +681,6 @@
       <c r="B31">
         <v>4.93</v>
       </c>
-      <c r="F31" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -786,9 +691,6 @@
       <c r="B32">
         <v>4.82</v>
       </c>
-      <c r="F32" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -798,9 +700,6 @@
       </c>
       <c r="B33">
         <v>4.46</v>
-      </c>
-      <c r="F33" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
